--- a/survey_templates/038_parent_reader_favorites_survey--survey_templates.xlsx
+++ b/survey_templates/038_parent_reader_favorites_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -799,7 +799,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C43"/>
+  <dimension ref="A1:C41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
@@ -1002,12 +1002,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>horror</t>
+          <t>historical_fiction</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Horror</t>
+          <t>Historical Fiction</t>
         </is>
       </c>
     </row>
@@ -1019,46 +1019,46 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>historical_fiction</t>
+          <t>mystery/thriller</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Historical Fiction</t>
+          <t>Mystery/Thriller</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>reader_preferences_choices</t>
+          <t>reading_frequency_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>mystery/thriller</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Mystery/Thriller</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>reader_preferences_choices</t>
+          <t>reading_frequency_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>romance</t>
+          <t>several_times_a_week</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Romance</t>
+          <t>Several times a week</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>about_once_a_week</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Daily</t>
+          <t>About once a week</t>
         </is>
       </c>
     </row>
@@ -1087,12 +1087,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>several_times_a_week</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Several times a week</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -1104,46 +1104,46 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>about_once_a_week</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>About once a week</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>reading_frequency_choices</t>
+          <t>reading_time_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>rarely</t>
+          <t>morning</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Rarely</t>
+          <t>Morning</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>reading_frequency_choices</t>
+          <t>reading_time_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>never</t>
+          <t>afternoon</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Never</t>
+          <t>Afternoon</t>
         </is>
       </c>
     </row>
@@ -1155,12 +1155,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>morning</t>
+          <t>evening</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Evening</t>
         </is>
       </c>
     </row>
@@ -1172,46 +1172,46 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>afternoon</t>
+          <t>late_night</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Afternoon</t>
+          <t>Late Night</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>reading_time_choices</t>
+          <t>family_reading_habits_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>evening</t>
+          <t>we_read_together</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Evening</t>
+          <t>We read together</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>reading_time_choices</t>
+          <t>family_reading_habits_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>late_night</t>
+          <t>we_read_separately</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Late Night</t>
+          <t>We read separately</t>
         </is>
       </c>
     </row>
@@ -1223,12 +1223,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>we_read_together</t>
+          <t>we_read_together_sometimes</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>We read together</t>
+          <t>We read together sometimes</t>
         </is>
       </c>
     </row>
@@ -1240,46 +1240,46 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>we_read_separately</t>
+          <t>none_of_the_above</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>We read separately</t>
+          <t>None of the above</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>family_reading_habits_choices</t>
+          <t>favorite_authors_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>we_read_together_sometimes</t>
+          <t>author_1</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>We read together sometimes</t>
+          <t>Author 1</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>family_reading_habits_choices</t>
+          <t>favorite_authors_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>none_of_the_above</t>
+          <t>author_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>None of the above</t>
+          <t>Author 2</t>
         </is>
       </c>
     </row>
@@ -1291,12 +1291,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>author_1</t>
+          <t>author_3</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Author 1</t>
+          <t>Author 3</t>
         </is>
       </c>
     </row>
@@ -1308,46 +1308,46 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>author_2</t>
+          <t>author_4</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Author 2</t>
+          <t>Author 4</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>favorite_authors_choices</t>
+          <t>recommended_books_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>author_3</t>
+          <t>book_1</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Author 3</t>
+          <t>Book 1</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>favorite_authors_choices</t>
+          <t>recommended_books_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>author_4</t>
+          <t>book_2</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Author 4</t>
+          <t>Book 2</t>
         </is>
       </c>
     </row>
@@ -1359,12 +1359,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>book_1</t>
+          <t>book_3</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Book 1</t>
+          <t>Book 3</t>
         </is>
       </c>
     </row>
@@ -1376,46 +1376,46 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>book_2</t>
+          <t>book_4</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Book 2</t>
+          <t>Book 4</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>recommended_books_choices</t>
+          <t>reading_device_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>book_3</t>
+          <t>physical_book</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Book 3</t>
+          <t>Physical book</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>recommended_books_choices</t>
+          <t>reading_device_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>book_4</t>
+          <t>e-reader</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Book 4</t>
+          <t>E-Reader</t>
         </is>
       </c>
     </row>
@@ -1427,12 +1427,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>physical_book</t>
+          <t>tablet</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Physical book</t>
+          <t>Tablet</t>
         </is>
       </c>
     </row>
@@ -1444,12 +1444,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>e-reader</t>
+          <t>smartphone</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>E-Reader</t>
+          <t>Smartphone</t>
         </is>
       </c>
     </row>
@@ -1461,78 +1461,44 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>tablet</t>
+          <t>computer</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Tablet</t>
+          <t>Computer</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>reading_device_choices</t>
+          <t>reading_habit_other_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>smartphone</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Smartphone</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>reading_device_choices</t>
+          <t>reading_habit_other_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>computer</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
-        <is>
-          <t>Computer</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>reading_habit_other_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>reading_habit_other_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
         <is>
           <t>None</t>
         </is>
